--- a/output/upload/S00027_1984_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
+++ b/output/upload/S00027_1984_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
@@ -2611,17 +2611,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>1984002</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>6415001</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">

--- a/output/upload/S00027_1984_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
+++ b/output/upload/S00027_1984_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
@@ -2628,29 +2628,29 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N7" s="6" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>

--- a/output/upload/S00027_1984_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
+++ b/output/upload/S00027_1984_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
@@ -2611,11 +2611,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>1984001</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>19841</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00027_1984_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
+++ b/output/upload/S00027_1984_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
@@ -2623,7 +2623,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>19841</t>
+          <t>1984001</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">

--- a/output/upload/S00027_1984_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
+++ b/output/upload/S00027_1984_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
@@ -2714,20 +2714,72 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
-      <c r="M8" s="6" t="n"/>
-      <c r="N8" s="6" t="n"/>
-      <c r="O8" s="6" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>1984002</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>1984002</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(종신갱신형)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="P8" s="6" t="n"/>
       <c r="Q8" s="6" t="n"/>
       <c r="R8" s="6" t="n"/>
@@ -2765,20 +2817,72 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
-      <c r="M9" s="6" t="n"/>
-      <c r="N9" s="6" t="n"/>
-      <c r="O9" s="6" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>1984003</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>1984003</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="P9" s="6" t="n"/>
       <c r="Q9" s="6" t="n"/>
       <c r="R9" s="6" t="n"/>
@@ -2816,20 +2920,72 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
-      <c r="M10" s="6" t="n"/>
-      <c r="N10" s="6" t="n"/>
-      <c r="O10" s="6" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>1984004</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>1984004</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="P10" s="6" t="n"/>
       <c r="Q10" s="6" t="n"/>
       <c r="R10" s="6" t="n"/>
@@ -2867,20 +3023,72 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
-      <c r="M11" s="6" t="n"/>
-      <c r="N11" s="6" t="n"/>
-      <c r="O11" s="6" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>1984005</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>1984005</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="P11" s="6" t="n"/>
       <c r="Q11" s="6" t="n"/>
       <c r="R11" s="6" t="n"/>
@@ -2918,20 +3126,72 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
-      <c r="M12" s="6" t="n"/>
-      <c r="N12" s="6" t="n"/>
-      <c r="O12" s="6" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>1984006</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>1984006</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(80세형)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="P12" s="6" t="n"/>
       <c r="Q12" s="6" t="n"/>
       <c r="R12" s="6" t="n"/>
@@ -2969,20 +3229,72 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
-      <c r="M13" s="6" t="n"/>
-      <c r="N13" s="6" t="n"/>
-      <c r="O13" s="6" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>1984007</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>1984007</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(상해급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="P13" s="6" t="n"/>
       <c r="Q13" s="6" t="n"/>
       <c r="R13" s="6" t="n"/>
@@ -3020,20 +3332,72 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
-      <c r="M14" s="6" t="n"/>
-      <c r="N14" s="6" t="n"/>
-      <c r="O14" s="6" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>1984008</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>1984008</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[개인중지재개용](갱신형) 무배당(질병급여형)(30세형)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="P14" s="6" t="n"/>
       <c r="Q14" s="6" t="n"/>
       <c r="R14" s="6" t="n"/>

--- a/output/upload/S00027_1984_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
+++ b/output/upload/S00027_1984_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
